--- a/Result/profitability/5220.xlsx
+++ b/Result/profitability/5220.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM55"/>
+  <dimension ref="A1:AM56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.13375</v>
+        <v>-0.08875</v>
       </c>
       <c r="N2" t="n">
-        <v>16.5</v>
+        <v>16.55625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.08</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.25125</v>
+        <v>-0.22125</v>
       </c>
       <c r="N3" t="n">
-        <v>14.95875</v>
+        <v>15.31</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.19125</v>
+        <v>-0.185</v>
       </c>
       <c r="N4" t="n">
-        <v>15.64125</v>
+        <v>15.1825</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,13 +914,13 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2999999999999999</v>
+        <v>-0.23375</v>
       </c>
       <c r="N5" t="n">
-        <v>14.175</v>
+        <v>14.25125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -7415,6 +7415,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>265</v>
+      </c>
+      <c r="D56" t="n">
+        <v>212</v>
+      </c>
+      <c r="E56" t="n">
+        <v>53</v>
+      </c>
+      <c r="F56" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="G56" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>4.60%</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>11</v>
+      </c>
+      <c r="K56" t="n">
+        <v>9</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="N56" t="n">
+        <v>18.63875</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="X56" t="n">
+        <v>-0.5111111111111111</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>-1.960000000000001</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-0.08953860210141618</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>-1.709677419354839</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.6099999999999994</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.03157349896480333</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
